--- a/data/config/aplicacoes_fundos.xlsx
+++ b/data/config/aplicacoes_fundos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos e Programação\Tesouraria\App Tesouraria Sementes Tropical\Código\data\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F02905-DA26-4DD7-991C-0CB38A365740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A81B27A-5098-44E3-888C-2336A2A55E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28740" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{7416F21D-5932-4029-913F-23D06D3BD085}"/>
+    <workbookView xWindow="-60" yWindow="-16425" windowWidth="29040" windowHeight="15840" xr2:uid="{7416F21D-5932-4029-913F-23D06D3BD085}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
   <si>
     <t xml:space="preserve">Conta </t>
   </si>
@@ -40,13 +40,53 @@
   </si>
   <si>
     <t>Data</t>
+  </si>
+  <si>
+    <t>BNP Paribas Match FIF RF CP RL</t>
+  </si>
+  <si>
+    <t>Aplicação</t>
+  </si>
+  <si>
+    <t>Bradesco Bancos II FIF CIC RF CP RL</t>
+  </si>
+  <si>
+    <t>Brave 90 FIC FIDC</t>
+  </si>
+  <si>
+    <t>JGP Crédito Ecossistema 360 Advisory FIC de FIF Multimercado CP RL</t>
+  </si>
+  <si>
+    <t>Jive BossaNova High Yield Advisory FIC FIDC</t>
+  </si>
+  <si>
+    <t>M8 Credit Opportunities FIC de FI em FIDC</t>
+  </si>
+  <si>
+    <t>Riza Daikon Advisory FIF em Cotas de FIM</t>
+  </si>
+  <si>
+    <t>Safra DI Master FIRF Referenciado DI LP</t>
+  </si>
+  <si>
+    <t>Solis Capital Antares Advisory FIC de FIDC</t>
+  </si>
+  <si>
+    <t>Trend Cash CIC de Classes RF Simples RL</t>
+  </si>
+  <si>
+    <t>Valora Horizon High Yield FIDC</t>
+  </si>
+  <si>
+    <t>XP Crédito Estruturado 120 FIC de FIF Multimercado CP RL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;R$&quot;\ #,##0.00;[Red]\-&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
@@ -86,10 +126,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -405,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA1C7B1-216A-4C6A-B3D2-C0F16635EE8F}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
@@ -432,88 +473,344 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C2" s="1"/>
-      <c r="E2" s="2"/>
+      <c r="A2">
+        <v>6445064</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2">
+        <v>500000</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="2"/>
+      <c r="A3">
+        <v>6445064</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2000000</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="2"/>
+      <c r="A4">
+        <v>6445064</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1">
+        <v>44944</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2">
+        <v>166139.65</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="2"/>
+      <c r="A5">
+        <v>6445064</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1">
+        <v>44699</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2">
+        <v>453870.66</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="2"/>
+      <c r="A6">
+        <v>6445064</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1">
+        <v>44761</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2">
+        <v>915429.86</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="2"/>
+      <c r="A7">
+        <v>6445064</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1">
+        <v>44771</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1844363.66</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="2"/>
+      <c r="A8">
+        <v>6445064</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1">
+        <v>44592</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2">
+        <v>672159.47</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="2"/>
+      <c r="A9">
+        <v>6445064</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1">
+        <v>44944</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1176822.9099999999</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="2"/>
+      <c r="A10">
+        <v>6445064</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1">
+        <v>44956</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2">
+        <v>490694.67</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
+      <c r="A11">
+        <v>6445064</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1">
+        <v>44972</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="2">
+        <v>326770.71000000002</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
+      <c r="A12">
+        <v>6445064</v>
+      </c>
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45001</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="2">
+        <v>756208.32</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
+      <c r="A13">
+        <v>6445064</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45310</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="2">
+        <v>121310.26</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="2"/>
+      <c r="A14">
+        <v>6445064</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1">
+        <v>44956</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="2">
+        <v>139968.29999999999</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
+      <c r="A15">
+        <v>6445064</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46212</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2800000</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="2"/>
+      <c r="A16">
+        <v>6445064</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1">
+        <v>45148</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="2">
+        <v>399756.08</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>6445064</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46150</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="2">
+        <v>90162.29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>6445064</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1">
+        <v>44784</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="2">
+        <v>955198.86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>6445064</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="1">
+        <v>44956</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1438679.38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>6445064</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1">
+        <v>45001</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="3">
+        <v>480945.94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>6445064</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="1">
+        <v>44456</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="3">
+        <v>430202.04</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
